--- a/main/ig/StructureDefinition-ActorXDS.xlsx
+++ b/main/ig/StructureDefinition-ActorXDS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T07:22:41+00:00</t>
+    <t>2026-09-24T12:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
